--- a/Invesco/Invesco-MSCI-USA.xlsx
+++ b/Invesco/Invesco-MSCI-USA.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Invesco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C650B75-EA8D-45DC-B8E9-268CDF269DEE}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A34140-3383-4E2F-98B2-B5E5F3581411}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="2265" windowWidth="27270" windowHeight="17505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs" sheetId="1" r:id="rId1"/>
     <sheet name="Performance" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,8 +36,32 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gerben van Loon</author>
+  </authors>
+  <commentList>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{9BE562CE-C897-402E-A07B-46579D214CE3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Pas vanaf hier neem ik weer transactiekosten mee</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>TER</t>
   </si>
@@ -81,9 +105,6 @@
     <t>2018 can't find swap fee</t>
   </si>
   <si>
-    <t>2021: can't find swap fee, got the number from the site</t>
-  </si>
-  <si>
     <t>Cost lowerings</t>
   </si>
   <si>
@@ -91,19 +112,30 @@
   </si>
   <si>
     <t>to 0,05%</t>
+  </si>
+  <si>
+    <t>After 2021: can't find swap fee, got the number from the site</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>KIID Transaction costs</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.000%"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +166,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -155,20 +194,19 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
   </cellXfs>
@@ -453,65 +491,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.234375" customWidth="1"/>
-    <col min="2" max="2" width="11.02734375" customWidth="1"/>
-    <col min="6" max="6" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.71875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.27734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16.27734375" customWidth="1"/>
-    <col min="12" max="12" width="20.17578125" customWidth="1"/>
-    <col min="13" max="13" width="13.44921875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="13" width="15.7109375" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="L1" s="8" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <v>2014</v>
+      </c>
+      <c r="C2" s="7">
+        <v>2015</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2017</v>
+      </c>
+      <c r="F2" s="7">
+        <v>2018</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2019</v>
+      </c>
+      <c r="H2" s="7">
+        <v>2020</v>
+      </c>
+      <c r="I2" s="7">
+        <v>2021</v>
+      </c>
+      <c r="J2" s="7">
+        <v>2022</v>
+      </c>
+      <c r="K2" s="7">
+        <v>2023</v>
+      </c>
+      <c r="L2" s="7">
+        <v>2024</v>
+      </c>
+      <c r="M2" s="7">
+        <v>2025</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>43102</v>
+      </c>
+      <c r="R2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B2" s="8">
-        <v>2014</v>
-      </c>
-      <c r="C2" s="8">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="8">
-        <v>2016</v>
-      </c>
-      <c r="E2" s="8">
-        <v>2017</v>
-      </c>
-      <c r="F2" s="8">
-        <v>2018</v>
-      </c>
-      <c r="G2" s="8">
-        <v>2019</v>
-      </c>
-      <c r="H2" s="8">
-        <v>2020</v>
-      </c>
-      <c r="I2" s="8">
-        <v>2021</v>
-      </c>
-      <c r="J2" s="8">
-        <v>2022</v>
-      </c>
-      <c r="L2" s="3">
-        <v>43102</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1">
@@ -529,7 +575,7 @@
       <c r="F3" s="1">
         <v>1.9E-3</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <f>((5/12)*0.19%)+((7/12)*0.05%)</f>
         <v>1.0833333333333333E-3</v>
       </c>
@@ -542,59 +588,80 @@
       <c r="J3" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="L3" s="3">
+      <c r="K3" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="L3" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="M3" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q3" s="3">
         <v>43613</v>
       </c>
-      <c r="M3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="R3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
+        <f>Performance!D15</f>
+        <v>0.12684074625681874</v>
+      </c>
+      <c r="C4" s="1">
+        <f>Performance!D14</f>
+        <v>6.995604773747467E-3</v>
+      </c>
+      <c r="D4" s="1">
+        <f>Performance!D13</f>
+        <v>0.10907265815215068</v>
+      </c>
+      <c r="E4" s="1">
         <f>Performance!D12</f>
-        <v>0.12684074625681874</v>
-      </c>
-      <c r="C4" s="1">
+        <v>0.21178567239535101</v>
+      </c>
+      <c r="F4" s="1">
         <f>Performance!D11</f>
-        <v>6.995604773747467E-3</v>
-      </c>
-      <c r="D4" s="1">
+        <v>-4.6835068152760437E-2</v>
+      </c>
+      <c r="G4" s="1">
         <f>Performance!D10</f>
-        <v>0.10907265815215068</v>
-      </c>
-      <c r="E4" s="1">
+        <v>0.31472954457270352</v>
+      </c>
+      <c r="H4" s="1">
         <f>Performance!D9</f>
-        <v>0.21178567239535101</v>
-      </c>
-      <c r="F4" s="1">
+        <v>0.21262192668662605</v>
+      </c>
+      <c r="I4" s="1">
         <f>Performance!D8</f>
-        <v>-4.6835068152760437E-2</v>
-      </c>
-      <c r="G4" s="1">
+        <v>0.26859062176466281</v>
+      </c>
+      <c r="J4" s="1">
         <f>Performance!D7</f>
-        <v>0.31472954457270352</v>
-      </c>
-      <c r="H4" s="1">
+        <v>-0.19533401629669486</v>
+      </c>
+      <c r="K4" s="1">
         <f>Performance!D6</f>
-        <v>0.21262192668662605</v>
-      </c>
-      <c r="I4" s="1">
+        <v>0.26950000000000002</v>
+      </c>
+      <c r="L4" s="1">
         <f>Performance!D5</f>
-        <v>0.26859062176466281</v>
-      </c>
-      <c r="J4" s="1">
+        <v>0.24940000000000001</v>
+      </c>
+      <c r="M4" s="1">
         <f>Performance!D4</f>
-        <v>-0.19533401629669486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+        <v>0.17610000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
@@ -624,9 +691,18 @@
       <c r="J5" s="1">
         <v>-0.1946</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="K5" s="1">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.25080000000000002</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.17749999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
@@ -665,12 +741,24 @@
         <f>J5-J4</f>
         <v>7.3401629669486712E-4</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="K6" s="1">
+        <f t="shared" ref="K6:M6" si="1">K5-K4</f>
+        <v>1.5000000000000013E-3</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="1"/>
+        <v>1.4000000000000123E-3</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="1"/>
+        <v>1.3999999999999846E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
@@ -678,19 +766,19 @@
         <v>3.7592537431812593E-3</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" ref="C8:F8" si="1">C6-C3</f>
+        <f t="shared" ref="C8:F8" si="2">C6-C3</f>
         <v>3.2043952262525328E-3</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.027341847849311E-3</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.2143276046489901E-3</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.4931847239561554E-5</v>
       </c>
       <c r="G8" s="1">
@@ -698,16 +786,35 @@
         <v>2.519384151813923E-4</v>
       </c>
       <c r="H8" s="1">
-        <f>H6-H3-H17</f>
+        <f t="shared" ref="H8:L8" si="3">H6-H3-H17</f>
         <v>1.7456441276590744E-4</v>
       </c>
       <c r="I8" s="1">
-        <f>I6-I3-I17</f>
+        <f t="shared" si="3"/>
         <v>2.0937823533718835E-4</v>
       </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J8" s="1">
+        <f t="shared" si="3"/>
+        <v>-6.5983703305132863E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="3"/>
+        <v>7.000000000000014E-4</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="3"/>
+        <v>6.0000000000001242E-4</v>
+      </c>
+      <c r="M8" s="1">
+        <f>M6-M3-M17-M19</f>
+        <v>-1.0000000000001533E-4</v>
+      </c>
+      <c r="O8" s="1">
+        <f>AVERAGE(F8:M8)</f>
+        <v>2.1312068909247402E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -717,8 +824,11 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -728,8 +838,11 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -739,30 +852,44 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>2019</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>2020</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>2021</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="L12" t="s">
+      <c r="J12" s="7">
+        <v>2022</v>
+      </c>
+      <c r="K12" s="7">
+        <v>2023</v>
+      </c>
+      <c r="L12" s="7">
+        <v>2024</v>
+      </c>
+      <c r="M12" s="7">
+        <v>2025</v>
+      </c>
+      <c r="Q12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <f>((6/12)*0.19%)+((6/12)*0.05%)</f>
         <v>1.2000000000000001E-3</v>
       </c>
@@ -773,246 +900,342 @@
       <c r="I13" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="L13" t="s">
+      <c r="J13" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="K13" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="M13" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6">
         <v>92199</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>545356</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <v>1308526</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="L14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J14" s="6">
+        <v>1584473</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1722480</v>
+      </c>
+      <c r="L14" s="6">
+        <v>2452597</v>
+      </c>
+      <c r="M14" s="6"/>
+      <c r="Q14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6">
         <f>F14/F3</f>
         <v>0</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="6">
         <f>G14/G13</f>
         <v>76832500</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <f>H14/H13</f>
         <v>1090712000</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="6">
         <f>I14/I13</f>
         <v>2617052000</v>
       </c>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J15" s="6">
+        <f t="shared" ref="J15:M15" si="4">J14/J13</f>
+        <v>3168946000</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="4"/>
+        <v>3444960000</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="4"/>
+        <v>4905194000</v>
+      </c>
+      <c r="M15" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="6">
         <v>25753</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="6">
         <v>440112</v>
       </c>
-    </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G17" s="6">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="5">
         <f>G16/G15</f>
         <v>3.3518367878176552E-4</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <f>H16/H15</f>
         <v>4.0350890060804318E-4</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="J17" s="6"/>
+      <c r="J17" s="5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="M17" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="1">
+        <v>6.9999999999999999E-4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1586E305-5D1D-495E-B105-DF0B155455C9}">
-  <dimension ref="B2:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:D18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.71875" customWidth="1"/>
-    <col min="4" max="4" width="16.6796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.17610000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.24940000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.26950000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
         <v>44925</v>
       </c>
-      <c r="C4">
+      <c r="C7">
         <v>107.37309999999999</v>
       </c>
-      <c r="D4" s="4">
-        <f t="shared" ref="D4:D14" si="0">(C4-C5)/C5</f>
+      <c r="D7" s="4">
+        <f t="shared" ref="D7:D17" si="0">(C7-C8)/C8</f>
         <v>-0.19533401629669486</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
         <v>44561</v>
       </c>
-      <c r="C5">
+      <c r="C8">
         <v>133.43809999999999</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
         <v>0.26859062176466281</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="2">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
         <v>44196</v>
       </c>
-      <c r="C6">
+      <c r="C9">
         <v>105.1861</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D9" s="4">
         <f t="shared" si="0"/>
         <v>0.21262192668662605</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="2">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
         <v>43830</v>
       </c>
-      <c r="C7">
+      <c r="C10">
         <v>86.742699999999999</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
         <v>0.31472954457270352</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="2">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
         <v>43465</v>
       </c>
-      <c r="C8">
+      <c r="C11">
         <v>65.977599999999995</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D11" s="4">
         <f t="shared" si="0"/>
         <v>-4.6835068152760437E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="2">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
         <v>43098</v>
       </c>
-      <c r="C9">
+      <c r="C12">
         <v>69.219499999999996</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
         <v>0.21178567239535101</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="2">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
         <v>42734</v>
       </c>
-      <c r="C10">
+      <c r="C13">
         <v>57.121899999999997</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D13" s="4">
         <f t="shared" si="0"/>
         <v>0.10907265815215068</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="2">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="2">
         <v>42369</v>
       </c>
-      <c r="C11">
+      <c r="C14">
         <v>51.504199999999997</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
         <v>6.995604773747467E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="2">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="2">
         <v>42004</v>
       </c>
-      <c r="C12">
+      <c r="C15">
         <v>51.1464</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D15" s="4">
         <f t="shared" si="0"/>
         <v>0.12684074625681874</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="2">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="2">
         <v>41639</v>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>45.389200000000002</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
         <v>0.31696885817164716</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2">
         <v>41274</v>
       </c>
-      <c r="C14">
+      <c r="C17">
         <v>34.4649</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D17" s="4">
         <f t="shared" si="0"/>
         <v>0.14987255111300915</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
         <v>40907</v>
       </c>
-      <c r="C15">
+      <c r="C18">
         <v>29.972799999999999</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D18" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Invesco/Invesco-MSCI-USA.xlsx
+++ b/Invesco/Invesco-MSCI-USA.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="386" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A34140-3383-4E2F-98B2-B5E5F3581411}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs" sheetId="1" r:id="rId1"/>
